--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_antofagasta.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:08</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -685,7 +685,7 @@
         <v>0.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>-0.5</v>
@@ -708,10 +708,10 @@
         <v>-0.03</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="9">
@@ -731,7 +731,7 @@
         <v>-0.01</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.21</v>
@@ -792,7 +792,7 @@
         <v>0.2</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.28</v>
@@ -815,7 +815,7 @@
         <v>0.13</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.17</v>
@@ -884,10 +884,10 @@
         <v>-0.09</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="17">
@@ -907,7 +907,7 @@
         <v>-0.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.6</v>
@@ -953,7 +953,7 @@
         <v>0.16</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.1</v>
@@ -976,7 +976,7 @@
         <v>0.13</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.35</v>
@@ -999,7 +999,7 @@
         <v>0.09</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.18</v>
@@ -1022,10 +1022,10 @@
         <v>0.01</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="23">
@@ -1045,7 +1045,7 @@
         <v>-0.08</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.25</v>
@@ -1068,7 +1068,7 @@
         <v>-0.36</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>-0.33</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_antofagasta.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:59</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2020_antofagasta.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
